--- a/artfynd/A 63808-2023 artfynd.xlsx
+++ b/artfynd/A 63808-2023 artfynd.xlsx
@@ -2266,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117521521</v>
+        <v>117521296</v>
       </c>
       <c r="B17" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,30 +2278,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2309,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>874695</v>
+        <v>874588</v>
       </c>
       <c r="R17" t="n">
-        <v>7375875</v>
+        <v>7375870</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2372,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117523325</v>
+        <v>117521521</v>
       </c>
       <c r="B18" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,25 +2385,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2415,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>874585</v>
+        <v>874695</v>
       </c>
       <c r="R18" t="n">
-        <v>7375850</v>
+        <v>7375875</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2478,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117521603</v>
+        <v>117523325</v>
       </c>
       <c r="B19" t="n">
-        <v>78216</v>
+        <v>79590</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,25 +2491,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>874692</v>
+        <v>874585</v>
       </c>
       <c r="R19" t="n">
-        <v>7375796</v>
+        <v>7375850</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2584,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117521296</v>
+        <v>117521603</v>
       </c>
       <c r="B20" t="n">
-        <v>97753</v>
+        <v>78216</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,31 +2597,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>874588</v>
+        <v>874692</v>
       </c>
       <c r="R20" t="n">
-        <v>7375870</v>
+        <v>7375796</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>

--- a/artfynd/A 63808-2023 artfynd.xlsx
+++ b/artfynd/A 63808-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117521907</v>
+        <v>117521575</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>874587</v>
+        <v>874722</v>
       </c>
       <c r="R2" t="n">
-        <v>7375861</v>
+        <v>7375832</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117521774</v>
+        <v>117521696</v>
       </c>
       <c r="B3" t="n">
         <v>79561</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>874574</v>
+        <v>874575</v>
       </c>
       <c r="R3" t="n">
-        <v>7375872</v>
+        <v>7375867</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117521440</v>
+        <v>117521296</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +899,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>874679</v>
+        <v>874588</v>
       </c>
       <c r="R4" t="n">
-        <v>7375895</v>
+        <v>7375870</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -993,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117521696</v>
+        <v>117521847</v>
       </c>
       <c r="B5" t="n">
         <v>79561</v>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>874575</v>
+        <v>874586</v>
       </c>
       <c r="R5" t="n">
-        <v>7375867</v>
+        <v>7375850</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117521484</v>
+        <v>117523352</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>874644</v>
+        <v>874575</v>
       </c>
       <c r="R6" t="n">
-        <v>7375863</v>
+        <v>7375869</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1205,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117521847</v>
+        <v>117521907</v>
       </c>
       <c r="B7" t="n">
         <v>79561</v>
@@ -1248,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>874586</v>
+        <v>874587</v>
       </c>
       <c r="R7" t="n">
-        <v>7375850</v>
+        <v>7375861</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1311,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117521320</v>
+        <v>117523300</v>
       </c>
       <c r="B8" t="n">
-        <v>97753</v>
+        <v>57303</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,31 +1324,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1355,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>874515</v>
+        <v>874600</v>
       </c>
       <c r="R8" t="n">
-        <v>7375916</v>
+        <v>7375891</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1399,7 +1400,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117523144</v>
+        <v>117521603</v>
       </c>
       <c r="B9" t="n">
-        <v>78217</v>
+        <v>78216</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>874599</v>
+        <v>874692</v>
       </c>
       <c r="R9" t="n">
-        <v>7375982</v>
+        <v>7375796</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1517,17 +1517,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117523097</v>
+        <v>117521484</v>
       </c>
       <c r="B10" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>874580</v>
+        <v>874644</v>
       </c>
       <c r="R10" t="n">
-        <v>7375941</v>
+        <v>7375863</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1623,17 +1623,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117523125</v>
+        <v>117523244</v>
       </c>
       <c r="B11" t="n">
-        <v>78217</v>
+        <v>79465</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,25 +1642,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>874667</v>
+        <v>874616</v>
       </c>
       <c r="R11" t="n">
-        <v>7375828</v>
+        <v>7375860</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117523163</v>
+        <v>117521440</v>
       </c>
       <c r="B13" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>874678</v>
+        <v>874679</v>
       </c>
       <c r="R13" t="n">
-        <v>7375884</v>
+        <v>7375895</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117523300</v>
+        <v>117521774</v>
       </c>
       <c r="B14" t="n">
-        <v>57303</v>
+        <v>79561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,27 +1964,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1992,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>874600</v>
+        <v>874574</v>
       </c>
       <c r="R14" t="n">
-        <v>7375891</v>
+        <v>7375872</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2036,6 +2035,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117523352</v>
+        <v>117523190</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>56502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,26 +2070,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2097,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>874575</v>
+        <v>874675</v>
       </c>
       <c r="R15" t="n">
-        <v>7375869</v>
+        <v>7375844</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2141,7 +2146,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2160,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117521575</v>
+        <v>117523163</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>874722</v>
+        <v>874678</v>
       </c>
       <c r="R16" t="n">
-        <v>7375832</v>
+        <v>7375884</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2266,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117521296</v>
+        <v>117521521</v>
       </c>
       <c r="B17" t="n">
-        <v>97753</v>
+        <v>78480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,31 +2282,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2310,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>874588</v>
+        <v>874695</v>
       </c>
       <c r="R17" t="n">
-        <v>7375870</v>
+        <v>7375875</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2373,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117521521</v>
+        <v>117523221</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>96797</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,30 +2388,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2416,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>874695</v>
+        <v>874625</v>
       </c>
       <c r="R18" t="n">
-        <v>7375875</v>
+        <v>7375864</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2479,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117523325</v>
+        <v>117523125</v>
       </c>
       <c r="B19" t="n">
-        <v>79590</v>
+        <v>78217</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,25 +2495,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>874585</v>
+        <v>874667</v>
       </c>
       <c r="R19" t="n">
-        <v>7375850</v>
+        <v>7375828</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2585,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117521603</v>
+        <v>117521745</v>
       </c>
       <c r="B20" t="n">
-        <v>78216</v>
+        <v>79561</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2601,21 +2605,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2628,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>874692</v>
+        <v>874586</v>
       </c>
       <c r="R20" t="n">
-        <v>7375796</v>
+        <v>7375844</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2691,10 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117521344</v>
+        <v>117523097</v>
       </c>
       <c r="B21" t="n">
-        <v>90743</v>
+        <v>78217</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,25 +2707,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>874677</v>
+        <v>874580</v>
       </c>
       <c r="R21" t="n">
-        <v>7375846</v>
+        <v>7375941</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2797,10 +2801,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117521745</v>
+        <v>117521344</v>
       </c>
       <c r="B22" t="n">
-        <v>79561</v>
+        <v>90743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,25 +2813,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>874586</v>
+        <v>874677</v>
       </c>
       <c r="R22" t="n">
-        <v>7375844</v>
+        <v>7375846</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2903,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117521408</v>
+        <v>117523144</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>78217</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,39 +2919,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>874603</v>
+        <v>874599</v>
       </c>
       <c r="R23" t="n">
-        <v>7375885</v>
+        <v>7375982</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3018,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117523221</v>
+        <v>117521320</v>
       </c>
       <c r="B24" t="n">
-        <v>96797</v>
+        <v>97753</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,21 +3029,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>874625</v>
+        <v>874515</v>
       </c>
       <c r="R24" t="n">
-        <v>7375864</v>
+        <v>7375916</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3118,17 +3113,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117523190</v>
+        <v>117523325</v>
       </c>
       <c r="B25" t="n">
-        <v>56502</v>
+        <v>79590</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,31 +3136,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102613</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3173,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>874675</v>
+        <v>874585</v>
       </c>
       <c r="R25" t="n">
-        <v>7375844</v>
+        <v>7375850</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3217,6 +3207,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3228,17 +3219,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117523244</v>
+        <v>117521408</v>
       </c>
       <c r="B26" t="n">
-        <v>79465</v>
+        <v>97836</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3247,30 +3238,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>874616</v>
+        <v>874603</v>
       </c>
       <c r="R26" t="n">
-        <v>7375860</v>
+        <v>7375885</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>

--- a/artfynd/A 63808-2023 artfynd.xlsx
+++ b/artfynd/A 63808-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117521575</v>
+        <v>117521408</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>874722</v>
+        <v>874603</v>
       </c>
       <c r="R2" t="n">
-        <v>7375832</v>
+        <v>7375885</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117521696</v>
+        <v>117521484</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>78482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>874575</v>
+        <v>874644</v>
       </c>
       <c r="R3" t="n">
-        <v>7375867</v>
+        <v>7375863</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -880,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117521296</v>
+        <v>117521320</v>
       </c>
       <c r="B4" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>874588</v>
+        <v>874515</v>
       </c>
       <c r="R4" t="n">
-        <v>7375870</v>
+        <v>7375916</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -994,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117521847</v>
+        <v>117523097</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>78219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>874586</v>
+        <v>874580</v>
       </c>
       <c r="R5" t="n">
-        <v>7375850</v>
+        <v>7375941</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1100,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117523352</v>
+        <v>117523144</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>78219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>874575</v>
+        <v>874599</v>
       </c>
       <c r="R6" t="n">
-        <v>7375869</v>
+        <v>7375982</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1199,17 +1208,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117521907</v>
+        <v>117521696</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>874587</v>
+        <v>874575</v>
       </c>
       <c r="R7" t="n">
-        <v>7375861</v>
+        <v>7375867</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1312,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117523300</v>
+        <v>117521296</v>
       </c>
       <c r="B8" t="n">
-        <v>57303</v>
+        <v>97755</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,31 +1333,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>874600</v>
+        <v>874588</v>
       </c>
       <c r="R8" t="n">
-        <v>7375891</v>
+        <v>7375870</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1400,6 +1409,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1421,7 +1431,7 @@
         <v>117521603</v>
       </c>
       <c r="B9" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117521484</v>
+        <v>117523221</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>96799</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,30 +1546,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1567,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>874644</v>
+        <v>874625</v>
       </c>
       <c r="R10" t="n">
-        <v>7375863</v>
+        <v>7375864</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1630,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117523244</v>
+        <v>117523325</v>
       </c>
       <c r="B11" t="n">
-        <v>79465</v>
+        <v>79592</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1657,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>874616</v>
+        <v>874585</v>
       </c>
       <c r="R11" t="n">
-        <v>7375860</v>
+        <v>7375850</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1736,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117521871</v>
+        <v>117521847</v>
       </c>
       <c r="B12" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>874583</v>
+        <v>874586</v>
       </c>
       <c r="R12" t="n">
-        <v>7375854</v>
+        <v>7375850</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1842,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117521440</v>
+        <v>117523244</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>79467</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1865,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>874679</v>
+        <v>874616</v>
       </c>
       <c r="R13" t="n">
-        <v>7375895</v>
+        <v>7375860</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1948,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117521774</v>
+        <v>117523125</v>
       </c>
       <c r="B14" t="n">
-        <v>79561</v>
+        <v>78219</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>874574</v>
+        <v>874667</v>
       </c>
       <c r="R14" t="n">
-        <v>7375872</v>
+        <v>7375828</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2054,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117523190</v>
+        <v>117521521</v>
       </c>
       <c r="B15" t="n">
-        <v>56502</v>
+        <v>78482</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,35 +2077,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2102,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>874675</v>
+        <v>874695</v>
       </c>
       <c r="R15" t="n">
-        <v>7375844</v>
+        <v>7375875</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2146,6 +2152,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2157,17 +2164,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117523163</v>
+        <v>117521440</v>
       </c>
       <c r="B16" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2187,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>874678</v>
+        <v>874679</v>
       </c>
       <c r="R16" t="n">
-        <v>7375884</v>
+        <v>7375895</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2270,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117521521</v>
+        <v>117521745</v>
       </c>
       <c r="B17" t="n">
-        <v>78480</v>
+        <v>79563</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2293,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2313,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>874695</v>
+        <v>874586</v>
       </c>
       <c r="R17" t="n">
-        <v>7375875</v>
+        <v>7375844</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2376,10 +2383,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117523221</v>
+        <v>117521344</v>
       </c>
       <c r="B18" t="n">
-        <v>96797</v>
+        <v>90745</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,31 +2395,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2420,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>874625</v>
+        <v>874677</v>
       </c>
       <c r="R18" t="n">
-        <v>7375864</v>
+        <v>7375846</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2483,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117523125</v>
+        <v>117521575</v>
       </c>
       <c r="B19" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2526,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>874667</v>
+        <v>874722</v>
       </c>
       <c r="R19" t="n">
-        <v>7375828</v>
+        <v>7375832</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2582,17 +2588,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117521745</v>
+        <v>117521907</v>
       </c>
       <c r="B20" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2632,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>874586</v>
+        <v>874587</v>
       </c>
       <c r="R20" t="n">
-        <v>7375844</v>
+        <v>7375861</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2695,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117523097</v>
+        <v>117521774</v>
       </c>
       <c r="B21" t="n">
-        <v>78217</v>
+        <v>79563</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,21 +2717,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2738,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>874580</v>
+        <v>874574</v>
       </c>
       <c r="R21" t="n">
-        <v>7375941</v>
+        <v>7375872</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2801,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117521344</v>
+        <v>117521871</v>
       </c>
       <c r="B22" t="n">
-        <v>90743</v>
+        <v>79563</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2813,25 +2819,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2844,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>874677</v>
+        <v>874583</v>
       </c>
       <c r="R22" t="n">
-        <v>7375846</v>
+        <v>7375854</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2907,10 +2913,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117523144</v>
+        <v>117523190</v>
       </c>
       <c r="B23" t="n">
-        <v>78217</v>
+        <v>56503</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,30 +2925,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2950,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>874599</v>
+        <v>874675</v>
       </c>
       <c r="R23" t="n">
-        <v>7375982</v>
+        <v>7375844</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2994,7 +3005,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3006,17 +3016,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117521320</v>
+        <v>117523163</v>
       </c>
       <c r="B24" t="n">
-        <v>97753</v>
+        <v>78219</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,31 +3035,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3057,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>874515</v>
+        <v>874678</v>
       </c>
       <c r="R24" t="n">
-        <v>7375916</v>
+        <v>7375884</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3113,17 +3122,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117523325</v>
+        <v>117523352</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>79592</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3163,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>874585</v>
+        <v>874575</v>
       </c>
       <c r="R25" t="n">
-        <v>7375850</v>
+        <v>7375869</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3226,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117521408</v>
+        <v>117523300</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>57304</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3238,39 +3247,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3278,10 +3279,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>874603</v>
+        <v>874600</v>
       </c>
       <c r="R26" t="n">
-        <v>7375885</v>
+        <v>7375891</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3322,7 +3323,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
         <v>117901847</v>
       </c>
       <c r="B27" t="n">
-        <v>56502</v>
+        <v>56503</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 63808-2023 artfynd.xlsx
+++ b/artfynd/A 63808-2023 artfynd.xlsx
@@ -1747,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117521847</v>
+        <v>117523125</v>
       </c>
       <c r="B12" t="n">
-        <v>79563</v>
+        <v>78219</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>874586</v>
+        <v>874667</v>
       </c>
       <c r="R12" t="n">
-        <v>7375850</v>
+        <v>7375828</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117523244</v>
+        <v>117521847</v>
       </c>
       <c r="B13" t="n">
-        <v>79467</v>
+        <v>79563</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,25 +1865,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>874616</v>
+        <v>874586</v>
       </c>
       <c r="R13" t="n">
-        <v>7375860</v>
+        <v>7375850</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1952,17 +1952,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117523125</v>
+        <v>117523244</v>
       </c>
       <c r="B14" t="n">
-        <v>78219</v>
+        <v>79467</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,25 +1971,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>874667</v>
+        <v>874616</v>
       </c>
       <c r="R14" t="n">
-        <v>7375828</v>
+        <v>7375860</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117521774</v>
+        <v>117523190</v>
       </c>
       <c r="B21" t="n">
-        <v>79563</v>
+        <v>56503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2713,30 +2713,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>102613</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2744,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>874574</v>
+        <v>874675</v>
       </c>
       <c r="R21" t="n">
-        <v>7375872</v>
+        <v>7375844</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2788,7 +2793,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2800,14 +2804,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117521871</v>
+        <v>117521774</v>
       </c>
       <c r="B22" t="n">
         <v>79563</v>
@@ -2850,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>874583</v>
+        <v>874574</v>
       </c>
       <c r="R22" t="n">
-        <v>7375854</v>
+        <v>7375872</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2913,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117523190</v>
+        <v>117521871</v>
       </c>
       <c r="B23" t="n">
-        <v>56503</v>
+        <v>79563</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,35 +2929,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2961,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>874675</v>
+        <v>874583</v>
       </c>
       <c r="R23" t="n">
-        <v>7375844</v>
+        <v>7375854</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3005,6 +3004,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 63808-2023 artfynd.xlsx
+++ b/artfynd/A 63808-2023 artfynd.xlsx
@@ -3021,11 +3021,11 @@
         <v>117523190</v>
       </c>
       <c r="B24" t="n">
-        <v>56503</v>
+        <v>56596</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3344,11 +3344,11 @@
         <v>117901847</v>
       </c>
       <c r="B27" t="n">
-        <v>56505</v>
+        <v>56596</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">

--- a/artfynd/A 63808-2023 artfynd.xlsx
+++ b/artfynd/A 63808-2023 artfynd.xlsx
@@ -3021,7 +3021,7 @@
         <v>117523190</v>
       </c>
       <c r="B24" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>117901847</v>
       </c>
       <c r="B27" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 63808-2023 artfynd.xlsx
+++ b/artfynd/A 63808-2023 artfynd.xlsx
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 63808-2023 artfynd.xlsx
+++ b/artfynd/A 63808-2023 artfynd.xlsx
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
